--- a/research/traditional_assets/database/data/denmark/denmark_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ8"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.01786</v>
+        <v>-0.0261</v>
       </c>
       <c r="E2">
-        <v>0.0321</v>
+        <v>0.032405</v>
       </c>
       <c r="F2">
-        <v>0.708</v>
+        <v>0.075</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>2494.8</v>
+        <v>-61.10000000000004</v>
       </c>
       <c r="L2">
-        <v>0.2535365853658537</v>
+        <v>-0.007618643856455278</v>
       </c>
       <c r="M2">
-        <v>1025.213</v>
+        <v>2174.7</v>
       </c>
       <c r="N2">
-        <v>0.04894692868123788</v>
+        <v>0.09065442767279866</v>
       </c>
       <c r="O2">
-        <v>0.4109399551066217</v>
+        <v>-35.59247135842878</v>
       </c>
       <c r="P2">
-        <v>347.55</v>
+        <v>463.5</v>
       </c>
       <c r="Q2">
-        <v>0.01659314216964107</v>
+        <v>0.01932143616422595</v>
       </c>
       <c r="R2">
-        <v>0.1393097643097643</v>
+        <v>-7.585924713584284</v>
       </c>
       <c r="S2">
-        <v>677.663</v>
+        <v>1711.2</v>
       </c>
       <c r="T2">
-        <v>0.6609972756880765</v>
+        <v>0.7868671540902193</v>
       </c>
       <c r="U2">
-        <v>21436.3</v>
+        <v>30278.6</v>
       </c>
       <c r="V2">
-        <v>1.023437127006407</v>
+        <v>1.262192097178278</v>
       </c>
       <c r="W2">
-        <v>0.09471727515302134</v>
+        <v>0.06596638655462185</v>
       </c>
       <c r="X2">
-        <v>0.064848467567652</v>
+        <v>0.09678591196416159</v>
       </c>
       <c r="Y2">
-        <v>0.02986880758536933</v>
+        <v>-0.03081952540953974</v>
       </c>
       <c r="Z2">
-        <v>0.03175109208913797</v>
+        <v>0.02311472655201822</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03809243035598577</v>
+        <v>0.06106287008034558</v>
       </c>
       <c r="AC2">
-        <v>-0.03809243035598577</v>
+        <v>-0.06106287008034558</v>
       </c>
       <c r="AD2">
-        <v>332599</v>
+        <v>296139.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>332599</v>
+        <v>296139.7</v>
       </c>
       <c r="AG2">
-        <v>311162.7</v>
+        <v>265861.1</v>
       </c>
       <c r="AH2">
-        <v>0.9407559559704523</v>
+        <v>0.925064802082663</v>
       </c>
       <c r="AI2">
-        <v>0.9003748234301732</v>
+        <v>0.9128542924139063</v>
       </c>
       <c r="AJ2">
-        <v>0.9369319808821284</v>
+        <v>0.9172368466448162</v>
       </c>
       <c r="AK2">
-        <v>0.8942374260807791</v>
+        <v>0.9038833231734993</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.028</v>
+        <v>0.0297</v>
       </c>
       <c r="E3">
-        <v>-0.0161</v>
+        <v>-0.00739</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,85 +731,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>193.1</v>
+        <v>209.2</v>
       </c>
       <c r="L3">
-        <v>0.2490648781116987</v>
+        <v>0.2877183331041122</v>
       </c>
       <c r="M3">
-        <v>151.5</v>
+        <v>166.4</v>
       </c>
       <c r="N3">
-        <v>0.0831275720164609</v>
+        <v>0.0701458561672709</v>
       </c>
       <c r="O3">
-        <v>0.7845675815639566</v>
+        <v>0.7954110898661568</v>
       </c>
       <c r="P3">
-        <v>38.5</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Q3">
-        <v>0.02112482853223594</v>
+        <v>0.03916195936261699</v>
       </c>
       <c r="R3">
-        <v>0.1993785603314345</v>
+        <v>0.4440726577437859</v>
       </c>
       <c r="S3">
-        <v>113</v>
+        <v>73.5</v>
       </c>
       <c r="T3">
-        <v>0.7458745874587459</v>
+        <v>0.4417067307692307</v>
       </c>
       <c r="U3">
-        <v>230.6</v>
+        <v>1710.5</v>
       </c>
       <c r="V3">
-        <v>0.1265294924554184</v>
+        <v>0.721060618834837</v>
       </c>
       <c r="W3">
-        <v>0.100155601659751</v>
+        <v>0.1013516786977375</v>
       </c>
       <c r="X3">
-        <v>0.07694121240180907</v>
+        <v>0.09678591196416159</v>
       </c>
       <c r="Y3">
-        <v>0.02321438925794196</v>
+        <v>0.004565766733575921</v>
       </c>
       <c r="Z3">
-        <v>0.1567592704921347</v>
+        <v>0.1296217064213641</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.03732930433810726</v>
+        <v>0.06034849336547819</v>
       </c>
       <c r="AC3">
-        <v>-0.03732930433810726</v>
+        <v>-0.06034849336547819</v>
       </c>
       <c r="AD3">
-        <v>3775.9</v>
+        <v>3685.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3775.9</v>
+        <v>3685.3</v>
       </c>
       <c r="AG3">
-        <v>3545.3</v>
+        <v>1974.8</v>
       </c>
       <c r="AH3">
-        <v>0.6744605601600457</v>
+        <v>0.6083862979777136</v>
       </c>
       <c r="AI3">
-        <v>0.6458172986471</v>
+        <v>0.6780930301023037</v>
       </c>
       <c r="AJ3">
-        <v>0.6604754275494616</v>
+        <v>0.4542903151598804</v>
       </c>
       <c r="AK3">
-        <v>0.6312743718950873</v>
+        <v>0.5302472947936525</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -826,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P/F BankNordik (CPSE:BNORDIK CSE)</t>
+          <t>Danske Bank A/S (CPSE:DANSKE)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -835,7 +835,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0842</v>
+        <v>-0.0315</v>
+      </c>
+      <c r="F4">
+        <v>0.075</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,85 +853,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>37.3</v>
+        <v>-736.1</v>
       </c>
       <c r="L4">
-        <v>0.5382395382395382</v>
+        <v>-0.1259754928806134</v>
       </c>
       <c r="M4">
-        <v>8.712999999999999</v>
+        <v>1334</v>
       </c>
       <c r="N4">
-        <v>0.04264806656877141</v>
+        <v>0.07949277175920959</v>
       </c>
       <c r="O4">
-        <v>0.2335924932975871</v>
+        <v>-1.812253769868224</v>
       </c>
       <c r="P4">
-        <v>8.529999999999999</v>
+        <v>224.7</v>
       </c>
       <c r="Q4">
-        <v>0.0417523250122369</v>
+        <v>0.01338982444849655</v>
       </c>
       <c r="R4">
-        <v>0.228686327077748</v>
+        <v>-0.3052574378481184</v>
       </c>
       <c r="S4">
-        <v>0.1829999999999998</v>
+        <v>1109.3</v>
       </c>
       <c r="T4">
-        <v>0.02100309881785836</v>
+        <v>0.831559220389805</v>
       </c>
       <c r="U4">
-        <v>169.1</v>
+        <v>17925.5</v>
       </c>
       <c r="V4">
-        <v>0.8277043563387175</v>
+        <v>1.068176671791388</v>
       </c>
       <c r="W4">
-        <v>0.09938715694111376</v>
+        <v>-0.0281801754896406</v>
       </c>
       <c r="X4">
-        <v>0.05275572273349492</v>
+        <v>0.3469104406643781</v>
       </c>
       <c r="Y4">
-        <v>0.04663143420761884</v>
+        <v>-0.3750906161540187</v>
       </c>
       <c r="Z4">
-        <v>0.3507085020242915</v>
+        <v>0.02173612216748182</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.03783649101712189</v>
+        <v>0.06062589352146264</v>
       </c>
       <c r="AC4">
-        <v>-0.03783649101712189</v>
+        <v>-0.06062589352146264</v>
       </c>
       <c r="AD4">
-        <v>155.3</v>
+        <v>231330.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>155.3</v>
+        <v>231330.9</v>
       </c>
       <c r="AG4">
-        <v>-13.79999999999998</v>
+        <v>213405.4</v>
       </c>
       <c r="AH4">
-        <v>0.4318687430478309</v>
+        <v>0.9323636917637699</v>
       </c>
       <c r="AI4">
-        <v>0.2803249097472925</v>
+        <v>0.9182100431536798</v>
       </c>
       <c r="AJ4">
-        <v>-0.07244094488188967</v>
+        <v>0.9270966015427471</v>
       </c>
       <c r="AK4">
-        <v>-0.03585346843335927</v>
+        <v>0.9119448505264489</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -945,7 +948,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sparekassen Sjælland-Fyn A/S (CPSE:SPKSJF)</t>
+          <t>P/F BankNordik (CPSE:BNORDIK CSE)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -954,10 +957,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0614</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="E5">
-        <v>0.146</v>
+        <v>0.073</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -972,85 +975,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>64.2</v>
+        <v>24.8</v>
       </c>
       <c r="L5">
-        <v>0.3248987854251013</v>
+        <v>0.4065573770491803</v>
       </c>
       <c r="M5">
-        <v>5.52</v>
+        <v>110.2</v>
       </c>
       <c r="N5">
-        <v>0.01276595744680851</v>
+        <v>0.5893048128342246</v>
       </c>
       <c r="O5">
-        <v>0.08598130841121494</v>
+        <v>4.443548387096774</v>
       </c>
       <c r="P5">
-        <v>3.81</v>
+        <v>110.2</v>
       </c>
       <c r="Q5">
-        <v>0.008811285846438484</v>
+        <v>0.5893048128342246</v>
       </c>
       <c r="R5">
-        <v>0.05934579439252336</v>
+        <v>4.443548387096774</v>
       </c>
       <c r="S5">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>0.3097826086956521</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>598.4</v>
+        <v>242.2</v>
       </c>
       <c r="V5">
-        <v>1.383903792784459</v>
+        <v>1.295187165775401</v>
       </c>
       <c r="W5">
-        <v>0.1220532319391635</v>
+        <v>0.06220215701028343</v>
       </c>
       <c r="X5">
-        <v>0.0510674220246304</v>
+        <v>0.08675683463634934</v>
       </c>
       <c r="Y5">
-        <v>0.0709858099145331</v>
+        <v>-0.02455467762606591</v>
       </c>
       <c r="Z5">
-        <v>0.6992215145081386</v>
+        <v>0.158482722785139</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.03790167013741946</v>
+        <v>0.06106287008034558</v>
       </c>
       <c r="AC5">
-        <v>-0.03790167013741946</v>
+        <v>-0.06106287008034558</v>
       </c>
       <c r="AD5">
-        <v>289.1</v>
+        <v>198.8</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>289.1</v>
+        <v>198.8</v>
       </c>
       <c r="AG5">
-        <v>-309.3</v>
+        <v>-43.39999999999998</v>
       </c>
       <c r="AH5">
-        <v>0.4006930006930007</v>
+        <v>0.5152928978745465</v>
       </c>
       <c r="AI5">
-        <v>0.3332949043117363</v>
+        <v>0.4418759724383197</v>
       </c>
       <c r="AJ5">
-        <v>-2.51259138911454</v>
+        <v>-0.3022284122562672</v>
       </c>
       <c r="AK5">
-        <v>-1.149814126394052</v>
+        <v>-0.2089552238805969</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1067,7 +1070,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Danske Bank A/S (CPSE:DANSKE)</t>
+          <t>Jyske Bank A/S (CPSE:JYSK)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1076,13 +1079,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.00991</v>
+        <v>-0.0261</v>
       </c>
       <c r="E6">
-        <v>-0.0561</v>
-      </c>
-      <c r="F6">
-        <v>0.708</v>
+        <v>-0.0353</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1097,85 +1097,85 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>1669.7</v>
+        <v>392.5</v>
       </c>
       <c r="L6">
-        <v>0.2325034115910547</v>
+        <v>0.3220116498482238</v>
       </c>
       <c r="M6">
-        <v>266.1</v>
+        <v>547.1999999999999</v>
       </c>
       <c r="N6">
-        <v>0.01813337331170867</v>
+        <v>0.1313458630373731</v>
       </c>
       <c r="O6">
-        <v>0.1593699466970115</v>
+        <v>1.394140127388535</v>
       </c>
       <c r="P6">
-        <v>266.1</v>
+        <v>18.8</v>
       </c>
       <c r="Q6">
-        <v>0.01813337331170867</v>
+        <v>0.004512613715465303</v>
       </c>
       <c r="R6">
-        <v>0.1593699466970115</v>
+        <v>0.04789808917197452</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>528.4</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>0.9656432748538013</v>
       </c>
       <c r="U6">
-        <v>8980.1</v>
+        <v>10063.5</v>
       </c>
       <c r="V6">
-        <v>0.6119485369277528</v>
+        <v>2.415568517318355</v>
       </c>
       <c r="W6">
-        <v>0.06719033573035336</v>
+        <v>0.06596638655462185</v>
       </c>
       <c r="X6">
-        <v>0.3561754260441353</v>
+        <v>0.3631212115331378</v>
       </c>
       <c r="Y6">
-        <v>-0.2889850903137819</v>
+        <v>-0.297154824978516</v>
       </c>
       <c r="Z6">
-        <v>0.03121267596084138</v>
+        <v>0.01696011888362929</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.03828319057455207</v>
+        <v>0.06199654679741819</v>
       </c>
       <c r="AC6">
-        <v>-0.03828319057455207</v>
+        <v>-0.06199654679741819</v>
       </c>
       <c r="AD6">
-        <v>252633.8</v>
+        <v>60732.1</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>252633.8</v>
+        <v>60732.1</v>
       </c>
       <c r="AG6">
-        <v>243653.7</v>
+        <v>50668.6</v>
       </c>
       <c r="AH6">
-        <v>0.9451023611678496</v>
+        <v>0.935805615564068</v>
       </c>
       <c r="AI6">
-        <v>0.9019543299440191</v>
+        <v>0.9218412508557056</v>
       </c>
       <c r="AJ6">
-        <v>0.943193989973224</v>
+        <v>0.9240243860183425</v>
       </c>
       <c r="AK6">
-        <v>0.8987067892366328</v>
+        <v>0.9077498575723156</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lån &amp; Spar Bank A/S (CPSE:LASP)</t>
+          <t>Sparekassen Sjælland-Fyn A/S (CPSE:SPKSJF)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1201,10 +1201,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0551</v>
+        <v>0.0441</v>
       </c>
       <c r="E7">
-        <v>0.05019999999999999</v>
+        <v>0.0722</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1219,212 +1219,90 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>28.5</v>
+        <v>48.5</v>
       </c>
       <c r="L7">
-        <v>0.1896207584830339</v>
+        <v>0.2859669811320755</v>
       </c>
       <c r="M7">
-        <v>6.18</v>
+        <v>16.9</v>
       </c>
       <c r="N7">
-        <v>0.01878990574642748</v>
+        <v>0.03504769805060141</v>
       </c>
       <c r="O7">
-        <v>0.2168421052631579</v>
+        <v>0.3484536082474227</v>
       </c>
       <c r="P7">
-        <v>4.31</v>
+        <v>16.9</v>
       </c>
       <c r="Q7">
-        <v>0.0131042870173305</v>
+        <v>0.03504769805060141</v>
       </c>
       <c r="R7">
-        <v>0.1512280701754386</v>
+        <v>0.3484536082474227</v>
       </c>
       <c r="S7">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>0.3025889967637541</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>1666.8</v>
+        <v>336.9</v>
       </c>
       <c r="V7">
-        <v>5.067801763453938</v>
+        <v>0.6986727498963086</v>
       </c>
       <c r="W7">
-        <v>0.09004739336492891</v>
+        <v>0.0838665052740792</v>
       </c>
       <c r="X7">
-        <v>0.0407015624877573</v>
+        <v>0.07318496844533867</v>
       </c>
       <c r="Y7">
-        <v>0.04934583087717161</v>
+        <v>0.01068153682874053</v>
       </c>
       <c r="Z7">
-        <v>-0.1643700787401575</v>
+        <v>0.6304832713754647</v>
       </c>
       <c r="AA7">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.03853831486348225</v>
+        <v>0.06282687638462109</v>
       </c>
       <c r="AC7">
-        <v>-0.03853831486348225</v>
+        <v>-0.06282687638462109</v>
       </c>
       <c r="AD7">
-        <v>35</v>
+        <v>192.6</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>35</v>
+        <v>192.6</v>
       </c>
       <c r="AG7">
-        <v>-1631.8</v>
+        <v>-144.3</v>
       </c>
       <c r="AH7">
-        <v>0.09618026930475405</v>
+        <v>0.2854179016004742</v>
       </c>
       <c r="AI7">
-        <v>0.09293680297397769</v>
+        <v>0.2720723265998022</v>
       </c>
       <c r="AJ7">
-        <v>1.252436871594136</v>
+        <v>-0.4270494229061852</v>
       </c>
       <c r="AK7">
-        <v>1.264765152689506</v>
+        <v>-0.3889487870619945</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Denmark</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Jyske Bank A/S (CPSE:JYSK)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>0.00772</v>
-      </c>
-      <c r="E8">
-        <v>0.0321</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>502</v>
-      </c>
-      <c r="L8">
-        <v>0.3424050201214106</v>
-      </c>
-      <c r="M8">
-        <v>587.1999999999999</v>
-      </c>
-      <c r="N8">
-        <v>0.1686048181008987</v>
-      </c>
-      <c r="O8">
-        <v>1.169721115537848</v>
-      </c>
-      <c r="P8">
-        <v>26.3</v>
-      </c>
-      <c r="Q8">
-        <v>0.007551612254859736</v>
-      </c>
-      <c r="R8">
-        <v>0.05239043824701196</v>
-      </c>
-      <c r="S8">
-        <v>560.9</v>
-      </c>
-      <c r="T8">
-        <v>0.9552111716621254</v>
-      </c>
-      <c r="U8">
-        <v>9791.299999999999</v>
-      </c>
-      <c r="V8">
-        <v>2.811410687110575</v>
-      </c>
-      <c r="W8">
-        <v>0.08880711872202665</v>
-      </c>
-      <c r="X8">
-        <v>0.4395762477107611</v>
-      </c>
-      <c r="Y8">
-        <v>-0.3507691289887345</v>
-      </c>
-      <c r="Z8">
-        <v>0.0194651046078434</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0.03907730308868645</v>
-      </c>
-      <c r="AC8">
-        <v>-0.03907730308868645</v>
-      </c>
-      <c r="AD8">
-        <v>75709.89999999999</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>75709.89999999999</v>
-      </c>
-      <c r="AG8">
-        <v>65918.59999999999</v>
-      </c>
-      <c r="AH8">
-        <v>0.9560224061339064</v>
-      </c>
-      <c r="AI8">
-        <v>0.9271368199079352</v>
-      </c>
-      <c r="AJ8">
-        <v>0.9498179428915597</v>
-      </c>
-      <c r="AK8">
-        <v>0.9172100193965097</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/denmark/denmark_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0261</v>
+        <v>0.0741</v>
       </c>
       <c r="E2">
-        <v>0.032405</v>
+        <v>0.153</v>
       </c>
       <c r="F2">
-        <v>0.075</v>
+        <v>0.242</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>-61.10000000000004</v>
+        <v>4131.4</v>
       </c>
       <c r="L2">
-        <v>-0.007618643856455278</v>
+        <v>0.376187137484862</v>
       </c>
       <c r="M2">
-        <v>2174.7</v>
+        <v>1423.6133</v>
       </c>
       <c r="N2">
-        <v>0.09065442767279866</v>
+        <v>0.0463397686288296</v>
       </c>
       <c r="O2">
-        <v>-35.59247135842878</v>
+        <v>0.3445837488502687</v>
       </c>
       <c r="P2">
-        <v>463.5</v>
+        <v>1065.8133</v>
       </c>
       <c r="Q2">
-        <v>0.01932143616422595</v>
+        <v>0.03469308816061872</v>
       </c>
       <c r="R2">
-        <v>-7.585924713584284</v>
+        <v>0.2579787239192526</v>
       </c>
       <c r="S2">
-        <v>1711.2</v>
+        <v>357.8</v>
       </c>
       <c r="T2">
-        <v>0.7868671540902193</v>
+        <v>0.2513322964880983</v>
       </c>
       <c r="U2">
-        <v>30278.6</v>
+        <v>33031.3</v>
       </c>
       <c r="V2">
-        <v>1.262192097178278</v>
+        <v>1.075195630379022</v>
       </c>
       <c r="W2">
-        <v>0.06596638655462185</v>
+        <v>0.1541218637992832</v>
       </c>
       <c r="X2">
-        <v>0.09678591196416159</v>
+        <v>0.08074774745307517</v>
       </c>
       <c r="Y2">
-        <v>-0.03081952540953974</v>
+        <v>0.073374116346208</v>
       </c>
       <c r="Z2">
-        <v>0.02311472655201822</v>
+        <v>0.03741239480819262</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06106287008034558</v>
+        <v>0.05210334382257095</v>
       </c>
       <c r="AC2">
-        <v>-0.06106287008034558</v>
+        <v>-0.05210334382257095</v>
       </c>
       <c r="AD2">
-        <v>296139.7</v>
+        <v>308245.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>296139.7</v>
+        <v>308245.4</v>
       </c>
       <c r="AG2">
-        <v>265861.1</v>
+        <v>275214.1</v>
       </c>
       <c r="AH2">
-        <v>0.925064802082663</v>
+        <v>0.909368061632031</v>
       </c>
       <c r="AI2">
-        <v>0.9128542924139063</v>
+        <v>0.9025503393434957</v>
       </c>
       <c r="AJ2">
-        <v>0.9172368466448162</v>
+        <v>0.8995826895425274</v>
       </c>
       <c r="AK2">
-        <v>0.9038833231734993</v>
+        <v>0.8921161973680031</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sydbank A/S (CPSE:SYDB)</t>
+          <t>Jyske Bank A/S (CPSE:JYSK)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0297</v>
+        <v>0.0803</v>
       </c>
       <c r="E3">
-        <v>-0.00739</v>
+        <v>0.153</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,85 +731,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>209.2</v>
+        <v>803.4</v>
       </c>
       <c r="L3">
-        <v>0.2877183331041122</v>
+        <v>0.4069496504913382</v>
       </c>
       <c r="M3">
-        <v>166.4</v>
+        <v>274.9</v>
       </c>
       <c r="N3">
-        <v>0.0701458561672709</v>
+        <v>0.05959633186636894</v>
       </c>
       <c r="O3">
-        <v>0.7954110898661568</v>
+        <v>0.3421707742096092</v>
       </c>
       <c r="P3">
-        <v>92.90000000000001</v>
+        <v>22.6</v>
       </c>
       <c r="Q3">
-        <v>0.03916195936261699</v>
+        <v>0.004899516552127821</v>
       </c>
       <c r="R3">
-        <v>0.4440726577437859</v>
+        <v>0.02813044560617376</v>
       </c>
       <c r="S3">
-        <v>73.5</v>
+        <v>252.3</v>
       </c>
       <c r="T3">
-        <v>0.4417067307692307</v>
+        <v>0.9177882866496908</v>
       </c>
       <c r="U3">
-        <v>1710.5</v>
+        <v>12050.6</v>
       </c>
       <c r="V3">
-        <v>0.721060618834837</v>
+        <v>2.612482927569536</v>
       </c>
       <c r="W3">
-        <v>0.1013516786977375</v>
+        <v>0.1560242367746446</v>
       </c>
       <c r="X3">
-        <v>0.09678591196416159</v>
+        <v>0.2685101272308917</v>
       </c>
       <c r="Y3">
-        <v>0.004565766733575921</v>
+        <v>-0.1124858904562471</v>
       </c>
       <c r="Z3">
-        <v>0.1296217064213641</v>
+        <v>0.03536864584415724</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06034849336547819</v>
+        <v>0.05191857700237565</v>
       </c>
       <c r="AC3">
-        <v>-0.06034849336547819</v>
+        <v>-0.05191857700237565</v>
       </c>
       <c r="AD3">
-        <v>3685.3</v>
+        <v>69107.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3685.3</v>
+        <v>69107.7</v>
       </c>
       <c r="AG3">
-        <v>1974.8</v>
+        <v>57057.1</v>
       </c>
       <c r="AH3">
-        <v>0.6083862979777136</v>
+        <v>0.937429802334225</v>
       </c>
       <c r="AI3">
-        <v>0.6780930301023037</v>
+        <v>0.9161237040149851</v>
       </c>
       <c r="AJ3">
-        <v>0.4542903151598804</v>
+        <v>0.9252032599424679</v>
       </c>
       <c r="AK3">
-        <v>0.5302472947936525</v>
+        <v>0.9001771732116629</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -835,10 +835,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0315</v>
+        <v>0.0195</v>
+      </c>
+      <c r="E4">
+        <v>0.0283</v>
       </c>
       <c r="F4">
-        <v>0.075</v>
+        <v>0.242</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -853,85 +856,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>-736.1</v>
+        <v>2775</v>
       </c>
       <c r="L4">
-        <v>-0.1259754928806134</v>
+        <v>0.3614128311322967</v>
       </c>
       <c r="M4">
-        <v>1334</v>
+        <v>852.6</v>
       </c>
       <c r="N4">
-        <v>0.07949277175920959</v>
+        <v>0.03710715638015903</v>
       </c>
       <c r="O4">
-        <v>-1.812253769868224</v>
+        <v>0.3072432432432433</v>
       </c>
       <c r="P4">
-        <v>224.7</v>
+        <v>852.6</v>
       </c>
       <c r="Q4">
-        <v>0.01338982444849655</v>
+        <v>0.03710715638015903</v>
       </c>
       <c r="R4">
-        <v>-0.3052574378481184</v>
+        <v>0.3072432432432433</v>
       </c>
       <c r="S4">
-        <v>1109.3</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.831559220389805</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>17925.5</v>
+        <v>18630.6</v>
       </c>
       <c r="V4">
-        <v>1.068176671791388</v>
+        <v>0.81084751073914</v>
       </c>
       <c r="W4">
-        <v>-0.0281801754896406</v>
+        <v>0.1346701672821862</v>
       </c>
       <c r="X4">
-        <v>0.3469104406643781</v>
+        <v>0.2010836471340863</v>
       </c>
       <c r="Y4">
-        <v>-0.3750906161540187</v>
+        <v>-0.0664134798519001</v>
       </c>
       <c r="Z4">
-        <v>0.02173612216748182</v>
+        <v>0.03289271889495681</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06062589352146264</v>
+        <v>0.05206040897490438</v>
       </c>
       <c r="AC4">
-        <v>-0.06062589352146264</v>
+        <v>-0.05206040897490438</v>
       </c>
       <c r="AD4">
-        <v>231330.9</v>
+        <v>234547.8</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>231330.9</v>
+        <v>234547.8</v>
       </c>
       <c r="AG4">
-        <v>213405.4</v>
+        <v>215917.2</v>
       </c>
       <c r="AH4">
-        <v>0.9323636917637699</v>
+        <v>0.9107785861151074</v>
       </c>
       <c r="AI4">
-        <v>0.9182100431536798</v>
+        <v>0.9074556762455628</v>
       </c>
       <c r="AJ4">
-        <v>0.9270966015427471</v>
+        <v>0.9038204826494104</v>
       </c>
       <c r="AK4">
-        <v>0.9119448505264489</v>
+        <v>0.9002668063171263</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -948,7 +951,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P/F BankNordik (CPSE:BNORDIK CSE)</t>
+          <t>Sydbank A/S (CPSE:SYDB)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -957,10 +960,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.06610000000000001</v>
+        <v>0.109</v>
       </c>
       <c r="E5">
-        <v>0.073</v>
+        <v>0.193</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -975,85 +978,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>24.8</v>
+        <v>443.1</v>
       </c>
       <c r="L5">
-        <v>0.4065573770491803</v>
+        <v>0.4281986857363742</v>
       </c>
       <c r="M5">
-        <v>110.2</v>
+        <v>188.2</v>
       </c>
       <c r="N5">
-        <v>0.5893048128342246</v>
+        <v>0.07879422231526062</v>
       </c>
       <c r="O5">
-        <v>4.443548387096774</v>
+        <v>0.4247348228390882</v>
       </c>
       <c r="P5">
-        <v>110.2</v>
+        <v>136</v>
       </c>
       <c r="Q5">
-        <v>0.5893048128342246</v>
+        <v>0.05693950177935943</v>
       </c>
       <c r="R5">
-        <v>4.443548387096774</v>
+        <v>0.3069284585872263</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>52.19999999999999</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.2773645058448458</v>
       </c>
       <c r="U5">
-        <v>242.2</v>
+        <v>1585.5</v>
       </c>
       <c r="V5">
-        <v>1.295187165775401</v>
+        <v>0.6638057358174586</v>
       </c>
       <c r="W5">
-        <v>0.06220215701028343</v>
+        <v>0.2540419676642587</v>
       </c>
       <c r="X5">
-        <v>0.08675683463634934</v>
+        <v>0.08074774745307517</v>
       </c>
       <c r="Y5">
-        <v>-0.02455467762606591</v>
+        <v>0.1732942202111835</v>
       </c>
       <c r="Z5">
-        <v>0.158482722785139</v>
+        <v>0.2782468405485345</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06106287008034558</v>
+        <v>0.05210334382257095</v>
       </c>
       <c r="AC5">
-        <v>-0.06106287008034558</v>
+        <v>-0.05210334382257095</v>
       </c>
       <c r="AD5">
-        <v>198.8</v>
+        <v>4031.7</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>198.8</v>
+        <v>4031.7</v>
       </c>
       <c r="AG5">
-        <v>-43.39999999999998</v>
+        <v>2446.2</v>
       </c>
       <c r="AH5">
-        <v>0.5152928978745465</v>
+        <v>0.6279710912432634</v>
       </c>
       <c r="AI5">
-        <v>0.4418759724383197</v>
+        <v>0.6528117359413202</v>
       </c>
       <c r="AJ5">
-        <v>-0.3022284122562672</v>
+        <v>0.5059672782178832</v>
       </c>
       <c r="AK5">
-        <v>-0.2089552238805969</v>
+        <v>0.5328947368421053</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1070,7 +1073,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jyske Bank A/S (CPSE:JYSK)</t>
+          <t>P/F BankNordik (CPSE:BNORDIK CSE)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1079,10 +1082,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.0261</v>
+        <v>-0.0525</v>
       </c>
       <c r="E6">
-        <v>-0.0353</v>
+        <v>-0.023</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1097,85 +1100,85 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>392.5</v>
+        <v>38.7</v>
       </c>
       <c r="L6">
-        <v>0.3220116498482238</v>
+        <v>0.4574468085106383</v>
       </c>
       <c r="M6">
-        <v>547.1999999999999</v>
+        <v>35.3133</v>
       </c>
       <c r="N6">
-        <v>0.1313458630373731</v>
+        <v>0.1512346895074946</v>
       </c>
       <c r="O6">
-        <v>1.394140127388535</v>
+        <v>0.9124883720930231</v>
       </c>
       <c r="P6">
-        <v>18.8</v>
+        <v>35.3133</v>
       </c>
       <c r="Q6">
-        <v>0.004512613715465303</v>
+        <v>0.1512346895074946</v>
       </c>
       <c r="R6">
-        <v>0.04789808917197452</v>
+        <v>0.9124883720930231</v>
       </c>
       <c r="S6">
-        <v>528.4</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>0.9656432748538013</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>10063.5</v>
+        <v>229.3</v>
       </c>
       <c r="V6">
-        <v>2.415568517318355</v>
+        <v>0.9820128479657388</v>
       </c>
       <c r="W6">
-        <v>0.06596638655462185</v>
+        <v>0.1541218637992832</v>
       </c>
       <c r="X6">
-        <v>0.3631212115331378</v>
+        <v>0.06987582165258099</v>
       </c>
       <c r="Y6">
-        <v>-0.297154824978516</v>
+        <v>0.08424604214670217</v>
       </c>
       <c r="Z6">
-        <v>0.01696011888362929</v>
+        <v>0.4073182474723158</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.06199654679741819</v>
+        <v>0.05324544615288605</v>
       </c>
       <c r="AC6">
-        <v>-0.06199654679741819</v>
+        <v>-0.05324544615288605</v>
       </c>
       <c r="AD6">
-        <v>60732.1</v>
+        <v>214.4</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>60732.1</v>
+        <v>214.4</v>
       </c>
       <c r="AG6">
-        <v>50668.6</v>
+        <v>-14.90000000000001</v>
       </c>
       <c r="AH6">
-        <v>0.935805615564068</v>
+        <v>0.4786782764009824</v>
       </c>
       <c r="AI6">
-        <v>0.9218412508557056</v>
+        <v>0.4392542511780373</v>
       </c>
       <c r="AJ6">
-        <v>0.9240243860183425</v>
+        <v>-0.06816102470265327</v>
       </c>
       <c r="AK6">
-        <v>0.9077498575723156</v>
+        <v>-0.05757341576506959</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1201,10 +1204,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0441</v>
+        <v>0.0741</v>
       </c>
       <c r="E7">
-        <v>0.0722</v>
+        <v>0.173</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1219,85 +1222,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>48.5</v>
+        <v>71.2</v>
       </c>
       <c r="L7">
-        <v>0.2859669811320755</v>
+        <v>0.3382422802850357</v>
       </c>
       <c r="M7">
-        <v>16.9</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="N7">
-        <v>0.03504769805060141</v>
+        <v>0.1424087877599058</v>
       </c>
       <c r="O7">
-        <v>0.3484536082474227</v>
+        <v>1.019662921348314</v>
       </c>
       <c r="P7">
-        <v>16.9</v>
+        <v>19.3</v>
       </c>
       <c r="Q7">
-        <v>0.03504769805060141</v>
+        <v>0.03785798352295017</v>
       </c>
       <c r="R7">
-        <v>0.3484536082474227</v>
+        <v>0.2710674157303371</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>53.3</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>0.7341597796143251</v>
       </c>
       <c r="U7">
-        <v>336.9</v>
+        <v>535.3</v>
       </c>
       <c r="V7">
-        <v>0.6986727498963086</v>
+        <v>1.050019615535504</v>
       </c>
       <c r="W7">
-        <v>0.0838665052740792</v>
+        <v>0.1381719386764992</v>
       </c>
       <c r="X7">
-        <v>0.07318496844533867</v>
+        <v>0.06643218009706423</v>
       </c>
       <c r="Y7">
-        <v>0.01068153682874053</v>
+        <v>0.07173975857943493</v>
       </c>
       <c r="Z7">
-        <v>0.6304832713754647</v>
+        <v>0.5673854447439353</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.06282687638462109</v>
+        <v>0.0538261907983638</v>
       </c>
       <c r="AC7">
-        <v>-0.06282687638462109</v>
+        <v>-0.0538261907983638</v>
       </c>
       <c r="AD7">
-        <v>192.6</v>
+        <v>343.8</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>192.6</v>
+        <v>343.8</v>
       </c>
       <c r="AG7">
-        <v>-144.3</v>
+        <v>-191.4999999999999</v>
       </c>
       <c r="AH7">
-        <v>0.2854179016004742</v>
+        <v>0.4027647610121837</v>
       </c>
       <c r="AI7">
-        <v>0.2720723265998022</v>
+        <v>0.3578640574581035</v>
       </c>
       <c r="AJ7">
-        <v>-0.4270494229061852</v>
+        <v>-0.6016336789192582</v>
       </c>
       <c r="AK7">
-        <v>-0.3889487870619945</v>
+        <v>-0.4501645510108132</v>
       </c>
       <c r="AL7">
         <v>0</v>

--- a/research/traditional_assets/database/data/denmark/denmark_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0741</v>
+        <v>0.09305000000000001</v>
       </c>
       <c r="E2">
-        <v>0.153</v>
+        <v>0.179</v>
       </c>
       <c r="F2">
-        <v>0.242</v>
+        <v>0.0555</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>4131.4</v>
+        <v>4373.3</v>
       </c>
       <c r="L2">
-        <v>0.376187137484862</v>
+        <v>0.3932788374205268</v>
       </c>
       <c r="M2">
-        <v>1423.6133</v>
+        <v>3154.3</v>
       </c>
       <c r="N2">
-        <v>0.0463397686288296</v>
+        <v>0.1128199809003995</v>
       </c>
       <c r="O2">
-        <v>0.3445837488502687</v>
+        <v>0.7212631193835318</v>
       </c>
       <c r="P2">
-        <v>1065.8133</v>
+        <v>2020.5</v>
       </c>
       <c r="Q2">
-        <v>0.03469308816061872</v>
+        <v>0.07226730856584893</v>
       </c>
       <c r="R2">
-        <v>0.2579787239192526</v>
+        <v>0.4620080945738915</v>
       </c>
       <c r="S2">
-        <v>357.8</v>
+        <v>1133.8</v>
       </c>
       <c r="T2">
-        <v>0.2513322964880983</v>
+        <v>0.3594458358431347</v>
       </c>
       <c r="U2">
-        <v>33031.3</v>
+        <v>35675.2</v>
       </c>
       <c r="V2">
-        <v>1.075195630379022</v>
+        <v>1.275996380375339</v>
       </c>
       <c r="W2">
-        <v>0.1541218637992832</v>
+        <v>0.1421962700421514</v>
       </c>
       <c r="X2">
-        <v>0.08074774745307517</v>
+        <v>0.2415509218221187</v>
       </c>
       <c r="Y2">
-        <v>0.073374116346208</v>
+        <v>-0.09935465177996733</v>
       </c>
       <c r="Z2">
-        <v>0.03741239480819262</v>
+        <v>0.03674886507504534</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05210334382257095</v>
+        <v>0.05560800602430833</v>
       </c>
       <c r="AC2">
-        <v>-0.05210334382257095</v>
+        <v>-0.05560800602430833</v>
       </c>
       <c r="AD2">
-        <v>308245.4</v>
+        <v>309269</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>308245.4</v>
+        <v>309269</v>
       </c>
       <c r="AG2">
-        <v>275214.1</v>
+        <v>273593.8</v>
       </c>
       <c r="AH2">
-        <v>0.909368061632031</v>
+        <v>0.9170925164213971</v>
       </c>
       <c r="AI2">
-        <v>0.9025503393434957</v>
+        <v>0.9013653571125672</v>
       </c>
       <c r="AJ2">
-        <v>0.8995826895425274</v>
+        <v>0.9072841379195994</v>
       </c>
       <c r="AK2">
-        <v>0.8921161973680031</v>
+        <v>0.8899197069964041</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0803</v>
+        <v>0.132</v>
       </c>
       <c r="E3">
-        <v>0.153</v>
+        <v>0.242</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,85 +731,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>803.4</v>
+        <v>873.7</v>
       </c>
       <c r="L3">
-        <v>0.4069496504913382</v>
+        <v>0.3949819168173599</v>
       </c>
       <c r="M3">
-        <v>274.9</v>
+        <v>678.1</v>
       </c>
       <c r="N3">
-        <v>0.05959633186636894</v>
+        <v>0.155720387636063</v>
       </c>
       <c r="O3">
-        <v>0.3421707742096092</v>
+        <v>0.7761245278699782</v>
       </c>
       <c r="P3">
-        <v>22.6</v>
+        <v>109.5</v>
       </c>
       <c r="Q3">
-        <v>0.004899516552127821</v>
+        <v>0.02514582280806503</v>
       </c>
       <c r="R3">
-        <v>0.02813044560617376</v>
+        <v>0.125329060318187</v>
       </c>
       <c r="S3">
-        <v>252.3</v>
+        <v>568.6</v>
       </c>
       <c r="T3">
-        <v>0.9177882866496908</v>
+        <v>0.8385193924199971</v>
       </c>
       <c r="U3">
-        <v>12050.6</v>
+        <v>10391.9</v>
       </c>
       <c r="V3">
-        <v>2.612482927569536</v>
+        <v>2.38641895926147</v>
       </c>
       <c r="W3">
-        <v>0.1560242367746446</v>
+        <v>0.1380863573144519</v>
       </c>
       <c r="X3">
-        <v>0.2685101272308917</v>
+        <v>0.287359506085172</v>
       </c>
       <c r="Y3">
-        <v>-0.1124858904562471</v>
+        <v>-0.1492731487707201</v>
       </c>
       <c r="Z3">
-        <v>0.03536864584415724</v>
+        <v>0.0348982318965422</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05191857700237565</v>
+        <v>0.05547088855885628</v>
       </c>
       <c r="AC3">
-        <v>-0.05191857700237565</v>
+        <v>-0.05547088855885628</v>
       </c>
       <c r="AD3">
-        <v>69107.7</v>
+        <v>73487.39999999999</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>69107.7</v>
+        <v>73487.39999999999</v>
       </c>
       <c r="AG3">
-        <v>57057.1</v>
+        <v>63095.49999999999</v>
       </c>
       <c r="AH3">
-        <v>0.937429802334225</v>
+        <v>0.9440584774286375</v>
       </c>
       <c r="AI3">
-        <v>0.9161237040149851</v>
+        <v>0.9087102757512056</v>
       </c>
       <c r="AJ3">
-        <v>0.9252032599424679</v>
+        <v>0.9354396805935055</v>
       </c>
       <c r="AK3">
-        <v>0.9001771732116629</v>
+        <v>0.8952497300579897</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0195</v>
+        <v>0.0541</v>
       </c>
       <c r="E4">
-        <v>0.0283</v>
+        <v>0.116</v>
       </c>
       <c r="F4">
-        <v>0.242</v>
+        <v>0.0555</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,456 +856,90 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>2775</v>
+        <v>3499.6</v>
       </c>
       <c r="L4">
-        <v>0.3614128311322967</v>
+        <v>0.39285594009946</v>
       </c>
       <c r="M4">
-        <v>852.6</v>
+        <v>2476.2</v>
       </c>
       <c r="N4">
-        <v>0.03710715638015903</v>
+        <v>0.1049055037048648</v>
       </c>
       <c r="O4">
-        <v>0.3072432432432433</v>
+        <v>0.7075665790376042</v>
       </c>
       <c r="P4">
-        <v>852.6</v>
+        <v>1911</v>
       </c>
       <c r="Q4">
-        <v>0.03710715638015903</v>
+        <v>0.08096051109764829</v>
       </c>
       <c r="R4">
-        <v>0.3072432432432433</v>
+        <v>0.5460624071322437</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>565.1999999999998</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.2282529682578143</v>
       </c>
       <c r="U4">
-        <v>18630.6</v>
+        <v>25283.3</v>
       </c>
       <c r="V4">
-        <v>0.81084751073914</v>
+        <v>1.071140183273245</v>
       </c>
       <c r="W4">
-        <v>0.1346701672821862</v>
+        <v>0.1463061827698508</v>
       </c>
       <c r="X4">
-        <v>0.2010836471340863</v>
+        <v>0.1957423375590654</v>
       </c>
       <c r="Y4">
-        <v>-0.0664134798519001</v>
+        <v>-0.04943615478921465</v>
       </c>
       <c r="Z4">
-        <v>0.03289271889495681</v>
+        <v>0.0372392280011772</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05206040897490438</v>
+        <v>0.05574512348976038</v>
       </c>
       <c r="AC4">
-        <v>-0.05206040897490438</v>
+        <v>-0.05574512348976038</v>
       </c>
       <c r="AD4">
-        <v>234547.8</v>
+        <v>235781.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>234547.8</v>
+        <v>235781.6</v>
       </c>
       <c r="AG4">
-        <v>215917.2</v>
+        <v>210498.3</v>
       </c>
       <c r="AH4">
-        <v>0.9107785861151074</v>
+        <v>0.9089999949881585</v>
       </c>
       <c r="AI4">
-        <v>0.9074556762455628</v>
+        <v>0.8991003337760547</v>
       </c>
       <c r="AJ4">
-        <v>0.9038204826494104</v>
+        <v>0.8991719008433916</v>
       </c>
       <c r="AK4">
-        <v>0.9002668063171263</v>
+        <v>0.8883344080648755</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Denmark</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Sydbank A/S (CPSE:SYDB)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>0.109</v>
-      </c>
-      <c r="E5">
-        <v>0.193</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>443.1</v>
-      </c>
-      <c r="L5">
-        <v>0.4281986857363742</v>
-      </c>
-      <c r="M5">
-        <v>188.2</v>
-      </c>
-      <c r="N5">
-        <v>0.07879422231526062</v>
-      </c>
-      <c r="O5">
-        <v>0.4247348228390882</v>
-      </c>
-      <c r="P5">
-        <v>136</v>
-      </c>
-      <c r="Q5">
-        <v>0.05693950177935943</v>
-      </c>
-      <c r="R5">
-        <v>0.3069284585872263</v>
-      </c>
-      <c r="S5">
-        <v>52.19999999999999</v>
-      </c>
-      <c r="T5">
-        <v>0.2773645058448458</v>
-      </c>
-      <c r="U5">
-        <v>1585.5</v>
-      </c>
-      <c r="V5">
-        <v>0.6638057358174586</v>
-      </c>
-      <c r="W5">
-        <v>0.2540419676642587</v>
-      </c>
-      <c r="X5">
-        <v>0.08074774745307517</v>
-      </c>
-      <c r="Y5">
-        <v>0.1732942202111835</v>
-      </c>
-      <c r="Z5">
-        <v>0.2782468405485345</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.05210334382257095</v>
-      </c>
-      <c r="AC5">
-        <v>-0.05210334382257095</v>
-      </c>
-      <c r="AD5">
-        <v>4031.7</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>4031.7</v>
-      </c>
-      <c r="AG5">
-        <v>2446.2</v>
-      </c>
-      <c r="AH5">
-        <v>0.6279710912432634</v>
-      </c>
-      <c r="AI5">
-        <v>0.6528117359413202</v>
-      </c>
-      <c r="AJ5">
-        <v>0.5059672782178832</v>
-      </c>
-      <c r="AK5">
-        <v>0.5328947368421053</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Denmark</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>P/F BankNordik (CPSE:BNORDIK CSE)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>-0.0525</v>
-      </c>
-      <c r="E6">
-        <v>-0.023</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>38.7</v>
-      </c>
-      <c r="L6">
-        <v>0.4574468085106383</v>
-      </c>
-      <c r="M6">
-        <v>35.3133</v>
-      </c>
-      <c r="N6">
-        <v>0.1512346895074946</v>
-      </c>
-      <c r="O6">
-        <v>0.9124883720930231</v>
-      </c>
-      <c r="P6">
-        <v>35.3133</v>
-      </c>
-      <c r="Q6">
-        <v>0.1512346895074946</v>
-      </c>
-      <c r="R6">
-        <v>0.9124883720930231</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>229.3</v>
-      </c>
-      <c r="V6">
-        <v>0.9820128479657388</v>
-      </c>
-      <c r="W6">
-        <v>0.1541218637992832</v>
-      </c>
-      <c r="X6">
-        <v>0.06987582165258099</v>
-      </c>
-      <c r="Y6">
-        <v>0.08424604214670217</v>
-      </c>
-      <c r="Z6">
-        <v>0.4073182474723158</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0.05324544615288605</v>
-      </c>
-      <c r="AC6">
-        <v>-0.05324544615288605</v>
-      </c>
-      <c r="AD6">
-        <v>214.4</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>214.4</v>
-      </c>
-      <c r="AG6">
-        <v>-14.90000000000001</v>
-      </c>
-      <c r="AH6">
-        <v>0.4786782764009824</v>
-      </c>
-      <c r="AI6">
-        <v>0.4392542511780373</v>
-      </c>
-      <c r="AJ6">
-        <v>-0.06816102470265327</v>
-      </c>
-      <c r="AK6">
-        <v>-0.05757341576506959</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Denmark</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Sparekassen Sjælland-Fyn A/S (CPSE:SPKSJF)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>0.0741</v>
-      </c>
-      <c r="E7">
-        <v>0.173</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>71.2</v>
-      </c>
-      <c r="L7">
-        <v>0.3382422802850357</v>
-      </c>
-      <c r="M7">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="N7">
-        <v>0.1424087877599058</v>
-      </c>
-      <c r="O7">
-        <v>1.019662921348314</v>
-      </c>
-      <c r="P7">
-        <v>19.3</v>
-      </c>
-      <c r="Q7">
-        <v>0.03785798352295017</v>
-      </c>
-      <c r="R7">
-        <v>0.2710674157303371</v>
-      </c>
-      <c r="S7">
-        <v>53.3</v>
-      </c>
-      <c r="T7">
-        <v>0.7341597796143251</v>
-      </c>
-      <c r="U7">
-        <v>535.3</v>
-      </c>
-      <c r="V7">
-        <v>1.050019615535504</v>
-      </c>
-      <c r="W7">
-        <v>0.1381719386764992</v>
-      </c>
-      <c r="X7">
-        <v>0.06643218009706423</v>
-      </c>
-      <c r="Y7">
-        <v>0.07173975857943493</v>
-      </c>
-      <c r="Z7">
-        <v>0.5673854447439353</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0.0538261907983638</v>
-      </c>
-      <c r="AC7">
-        <v>-0.0538261907983638</v>
-      </c>
-      <c r="AD7">
-        <v>343.8</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>343.8</v>
-      </c>
-      <c r="AG7">
-        <v>-191.4999999999999</v>
-      </c>
-      <c r="AH7">
-        <v>0.4027647610121837</v>
-      </c>
-      <c r="AI7">
-        <v>0.3578640574581035</v>
-      </c>
-      <c r="AJ7">
-        <v>-0.6016336789192582</v>
-      </c>
-      <c r="AK7">
-        <v>-0.4501645510108132</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/denmark/denmark_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.09305000000000001</v>
+        <v>0.106</v>
       </c>
       <c r="E2">
-        <v>0.179</v>
+        <v>0.242</v>
       </c>
       <c r="F2">
         <v>0.0555</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>4373.3</v>
+        <v>5013.8</v>
       </c>
       <c r="L2">
-        <v>0.3932788374205268</v>
+        <v>0.3970666265413278</v>
       </c>
       <c r="M2">
-        <v>3154.3</v>
+        <v>3637.9</v>
       </c>
       <c r="N2">
-        <v>0.1128199809003995</v>
+        <v>0.1155784162970682</v>
       </c>
       <c r="O2">
-        <v>0.7212631193835318</v>
+        <v>0.7255774063584506</v>
       </c>
       <c r="P2">
-        <v>2020.5</v>
+        <v>2314.9</v>
       </c>
       <c r="Q2">
-        <v>0.07226730856584893</v>
+        <v>0.07354585774377614</v>
       </c>
       <c r="R2">
-        <v>0.4620080945738915</v>
+        <v>0.4617056922892816</v>
       </c>
       <c r="S2">
-        <v>1133.8</v>
+        <v>1323</v>
       </c>
       <c r="T2">
-        <v>0.3594458358431347</v>
+        <v>0.3636713488551087</v>
       </c>
       <c r="U2">
-        <v>35675.2</v>
+        <v>37271.8</v>
       </c>
       <c r="V2">
-        <v>1.275996380375339</v>
+        <v>1.184148991599842</v>
       </c>
       <c r="W2">
-        <v>0.1421962700421514</v>
+        <v>0.1526989787647917</v>
       </c>
       <c r="X2">
-        <v>0.2415509218221187</v>
+        <v>0.08174618855217583</v>
       </c>
       <c r="Y2">
-        <v>-0.09935465177996733</v>
+        <v>0.07095279021261588</v>
       </c>
       <c r="Z2">
-        <v>0.03674886507504534</v>
+        <v>0.04101662740552965</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05560800602430833</v>
+        <v>0.05747529496602121</v>
       </c>
       <c r="AC2">
-        <v>-0.05560800602430833</v>
+        <v>-0.05747529496602121</v>
       </c>
       <c r="AD2">
-        <v>309269</v>
+        <v>313491.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>309269</v>
+        <v>313491.7</v>
       </c>
       <c r="AG2">
-        <v>273593.8</v>
+        <v>276219.9</v>
       </c>
       <c r="AH2">
-        <v>0.9170925164213971</v>
+        <v>0.9087577286310906</v>
       </c>
       <c r="AI2">
-        <v>0.9013653571125672</v>
+        <v>0.8939596102061808</v>
       </c>
       <c r="AJ2">
-        <v>0.9072841379195994</v>
+        <v>0.8977053613068765</v>
       </c>
       <c r="AK2">
-        <v>0.8899197069964041</v>
+        <v>0.8813487557190213</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -770,10 +770,10 @@
         <v>0.1380863573144519</v>
       </c>
       <c r="X3">
-        <v>0.287359506085172</v>
+        <v>0.2872042047999432</v>
       </c>
       <c r="Y3">
-        <v>-0.1492731487707201</v>
+        <v>-0.1491178474854913</v>
       </c>
       <c r="Z3">
         <v>0.0348982318965422</v>
@@ -782,10 +782,10 @@
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05547088855885628</v>
+        <v>0.05546220076850329</v>
       </c>
       <c r="AC3">
-        <v>-0.05547088855885628</v>
+        <v>-0.05546220076850329</v>
       </c>
       <c r="AD3">
         <v>73487.39999999999</v>
@@ -895,10 +895,10 @@
         <v>0.1463061827698508</v>
       </c>
       <c r="X4">
-        <v>0.1957423375590654</v>
+        <v>0.1956459379674678</v>
       </c>
       <c r="Y4">
-        <v>-0.04943615478921465</v>
+        <v>-0.04933975519761705</v>
       </c>
       <c r="Z4">
         <v>0.0372392280011772</v>
@@ -907,10 +907,10 @@
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05574512348976038</v>
+        <v>0.05573635112644186</v>
       </c>
       <c r="AC4">
-        <v>-0.05574512348976038</v>
+        <v>-0.05573635112644186</v>
       </c>
       <c r="AD4">
         <v>235781.6</v>
@@ -940,6 +940,372 @@
         <v>0</v>
       </c>
       <c r="AM4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Føroya Banki (CPSE:FOBANK)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>-0.0169</v>
+      </c>
+      <c r="E5">
+        <v>0.113</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>48.9</v>
+      </c>
+      <c r="L5">
+        <v>0.4944388270980788</v>
+      </c>
+      <c r="M5">
+        <v>13</v>
+      </c>
+      <c r="N5">
+        <v>0.06038086391082211</v>
+      </c>
+      <c r="O5">
+        <v>0.2658486707566462</v>
+      </c>
+      <c r="P5">
+        <v>13</v>
+      </c>
+      <c r="Q5">
+        <v>0.06038086391082211</v>
+      </c>
+      <c r="R5">
+        <v>0.2658486707566462</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>444.7</v>
+      </c>
+      <c r="V5">
+        <v>2.065490013934046</v>
+      </c>
+      <c r="W5">
+        <v>0.1786627694556083</v>
+      </c>
+      <c r="X5">
+        <v>0.08174618855217583</v>
+      </c>
+      <c r="Y5">
+        <v>0.0969165809034325</v>
+      </c>
+      <c r="Z5">
+        <v>0.3821483771251932</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.05747529496602121</v>
+      </c>
+      <c r="AC5">
+        <v>-0.05747529496602121</v>
+      </c>
+      <c r="AD5">
+        <v>306.1</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>306.1</v>
+      </c>
+      <c r="AG5">
+        <v>-138.6</v>
+      </c>
+      <c r="AH5">
+        <v>0.5870732642884541</v>
+      </c>
+      <c r="AI5">
+        <v>0.505282271376692</v>
+      </c>
+      <c r="AJ5">
+        <v>-1.807040417209907</v>
+      </c>
+      <c r="AK5">
+        <v>-0.8603351955307259</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Sydbank A/S (CPSE:SYDB)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.146</v>
+      </c>
+      <c r="E6">
+        <v>0.313</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>497.4</v>
+      </c>
+      <c r="L6">
+        <v>0.4331620656622834</v>
+      </c>
+      <c r="M6">
+        <v>419</v>
+      </c>
+      <c r="N6">
+        <v>0.1541688130105232</v>
+      </c>
+      <c r="O6">
+        <v>0.8423803779654202</v>
+      </c>
+      <c r="P6">
+        <v>251.3</v>
+      </c>
+      <c r="Q6">
+        <v>0.09246449334020163</v>
+      </c>
+      <c r="R6">
+        <v>0.5052271813429836</v>
+      </c>
+      <c r="S6">
+        <v>167.7</v>
+      </c>
+      <c r="T6">
+        <v>0.4002386634844868</v>
+      </c>
+      <c r="U6">
+        <v>285.1</v>
+      </c>
+      <c r="V6">
+        <v>0.1049010228861579</v>
+      </c>
+      <c r="W6">
+        <v>0.23258206303189</v>
+      </c>
+      <c r="X6">
+        <v>0.08016666238065556</v>
+      </c>
+      <c r="Y6">
+        <v>0.1524154006512345</v>
+      </c>
+      <c r="Z6">
+        <v>0.2504580352469029</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.05767012724570542</v>
+      </c>
+      <c r="AC6">
+        <v>-0.05767012724570542</v>
+      </c>
+      <c r="AD6">
+        <v>3541.1</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>3541.1</v>
+      </c>
+      <c r="AG6">
+        <v>3256</v>
+      </c>
+      <c r="AH6">
+        <v>0.5657703430315232</v>
+      </c>
+      <c r="AI6">
+        <v>0.6022791053661025</v>
+      </c>
+      <c r="AJ6">
+        <v>0.5450467039405403</v>
+      </c>
+      <c r="AK6">
+        <v>0.5820105820105821</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sparekassen Sjælland-Fyn A/S (CPSE:SPKSJF)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.106</v>
+      </c>
+      <c r="E7">
+        <v>0.252</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>94.2</v>
+      </c>
+      <c r="L7">
+        <v>0.3625866050808314</v>
+      </c>
+      <c r="M7">
+        <v>51.6</v>
+      </c>
+      <c r="N7">
+        <v>0.08838643371017472</v>
+      </c>
+      <c r="O7">
+        <v>0.5477707006369427</v>
+      </c>
+      <c r="P7">
+        <v>30.1</v>
+      </c>
+      <c r="Q7">
+        <v>0.05155875299760192</v>
+      </c>
+      <c r="R7">
+        <v>0.3195329087048832</v>
+      </c>
+      <c r="S7">
+        <v>21.5</v>
+      </c>
+      <c r="T7">
+        <v>0.4166666666666666</v>
+      </c>
+      <c r="U7">
+        <v>866.8</v>
+      </c>
+      <c r="V7">
+        <v>1.484755053100377</v>
+      </c>
+      <c r="W7">
+        <v>0.1526989787647917</v>
+      </c>
+      <c r="X7">
+        <v>0.07139572928153118</v>
+      </c>
+      <c r="Y7">
+        <v>0.08130324948326054</v>
+      </c>
+      <c r="Z7">
+        <v>0.6298181818181817</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.05926459788862494</v>
+      </c>
+      <c r="AC7">
+        <v>-0.05926459788862494</v>
+      </c>
+      <c r="AD7">
+        <v>375.5</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>375.5</v>
+      </c>
+      <c r="AG7">
+        <v>-491.3</v>
+      </c>
+      <c r="AH7">
+        <v>0.3914312519545502</v>
+      </c>
+      <c r="AI7">
+        <v>0.3474599796428241</v>
+      </c>
+      <c r="AJ7">
+        <v>-5.311351351351351</v>
+      </c>
+      <c r="AK7">
+        <v>-2.296867695184665</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
         <v>0</v>
       </c>
     </row>
